--- a/memo.xlsx
+++ b/memo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\plc_simulator\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5882E37-5F00-4A07-83B7-443B2D516F07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12D18E2C-350B-4CC0-99BB-7D889CDC1C7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{93724AB7-5517-49E2-875F-5FF3EE27D773}"/>
+    <workbookView xWindow="0" yWindow="240" windowWidth="19360" windowHeight="10480" xr2:uid="{93724AB7-5517-49E2-875F-5FF3EE27D773}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="10">
   <si>
     <t>コンポーネント</t>
     <phoneticPr fontId="1"/>
@@ -63,179 +63,134 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>命令入力後、エンター入力で反映</t>
-    <rPh sb="0" eb="5">
-      <t>メイレイニュウリョクゴ</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>ニュウリョク</t>
-    </rPh>
-    <rPh sb="13" eb="15">
-      <t>ハンエイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ctrl+↑キーで該当セルではなく隣のセルに線を引くようにする</t>
-    <rPh sb="9" eb="11">
-      <t>ガイトウ</t>
-    </rPh>
-    <rPh sb="17" eb="18">
-      <t>トナリ</t>
+    <t>9列目でctrl+→、2列目でctrl+←を押した際は線を引かないようにする</t>
+    <rPh sb="1" eb="3">
+      <t>レツメ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>レツメ</t>
     </rPh>
     <rPh sb="22" eb="23">
+      <t>オ</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>サイ</t>
+    </rPh>
+    <rPh sb="27" eb="28">
       <t>セン</t>
     </rPh>
-    <rPh sb="24" eb="25">
+    <rPh sb="29" eb="30">
       <t>ヒ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>複数セルの選択機能をつける</t>
+    <t>複数セル選択時、該当セル以外は枠線を引かずに塗りつぶしだけにする</t>
     <rPh sb="0" eb="2">
       <t>フクスウ</t>
     </rPh>
-    <rPh sb="5" eb="7">
-      <t>センタク</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>キノウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ctrl+xの切り取り機能をつける</t>
-    <rPh sb="7" eb="8">
-      <t>キ</t>
-    </rPh>
-    <rPh sb="9" eb="10">
-      <t>ト</t>
+    <rPh sb="4" eb="7">
+      <t>センタクジ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ガイトウ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>イガイ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ワクセン</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>ヒ</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>ヌ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>行番号、列番号の太字を解除する</t>
+    <rPh sb="0" eb="3">
+      <t>ギョウバンゴウ</t>
+    </rPh>
+    <rPh sb="4" eb="7">
+      <t>レツバンゴウ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>フトジ</t>
     </rPh>
     <rPh sb="11" eb="13">
-      <t>キノウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>複数セルのコピー、切り取り、削除機能をつける</t>
-    <rPh sb="0" eb="2">
-      <t>フクスウ</t>
-    </rPh>
-    <rPh sb="9" eb="10">
-      <t>キ</t>
+      <t>カイジョ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>行番号、列番号の背景を淡い色にして見た目をよくする</t>
+    <rPh sb="0" eb="3">
+      <t>ギョウバンゴウ</t>
+    </rPh>
+    <rPh sb="4" eb="7">
+      <t>レツバンゴウ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ハイケイ</t>
     </rPh>
     <rPh sb="11" eb="12">
-      <t>ト</t>
-    </rPh>
-    <rPh sb="14" eb="16">
-      <t>サクジョ</t>
-    </rPh>
-    <rPh sb="16" eb="18">
-      <t>キノウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ラダーの線がボーダーで途切れないようにする</t>
-    <rPh sb="4" eb="5">
+      <t>アワ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>イロ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>メ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ラダー部の一番左と一番右側の縦線は実線にする</t>
+    <rPh sb="3" eb="4">
+      <t>ブ</t>
+    </rPh>
+    <rPh sb="5" eb="8">
+      <t>イチバンヒダリ</t>
+    </rPh>
+    <rPh sb="9" eb="12">
+      <t>イチバンミギ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>ガワ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>タテ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
       <t>セン</t>
     </rPh>
-    <rPh sb="11" eb="13">
-      <t>トギ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ラダーの行番号を0埋め3桁にする</t>
-    <rPh sb="4" eb="7">
-      <t>ギョウバンゴウ</t>
-    </rPh>
-    <rPh sb="9" eb="10">
-      <t>ウ</t>
-    </rPh>
-    <rPh sb="12" eb="13">
-      <t>ケタ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>設備モデルを別ウインドウで開くようにする</t>
-    <rPh sb="0" eb="2">
-      <t>セツビ</t>
-    </rPh>
-    <rPh sb="6" eb="7">
-      <t>ベツ</t>
-    </rPh>
-    <rPh sb="13" eb="14">
-      <t>ヒラ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>タッチパネル</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>モデル</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>全体</t>
-    <rPh sb="0" eb="2">
-      <t>ゼンタイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ラダー・タッチパネルの外部データ保存・読込機能</t>
-    <rPh sb="11" eb="13">
-      <t>ガイブ</t>
-    </rPh>
-    <rPh sb="16" eb="18">
+    <rPh sb="17" eb="19">
+      <t>ジッセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>deviceListの表示有無ボタン、ラダーの保存、読み込みボタンをラダーポップアップウインドウの上部につける</t>
+    <rPh sb="11" eb="15">
+      <t>ヒョウジウム</t>
+    </rPh>
+    <rPh sb="23" eb="25">
       <t>ホゾン</t>
     </rPh>
-    <rPh sb="19" eb="21">
-      <t>ヨミコミ</t>
-    </rPh>
-    <rPh sb="21" eb="23">
-      <t>キノウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>部品を四角にしてUIを整える</t>
-    <rPh sb="0" eb="2">
-      <t>ブヒン</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>シカク</t>
-    </rPh>
-    <rPh sb="11" eb="12">
-      <t>トトノ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>文字表示コンポーネントを作成</t>
-    <rPh sb="0" eb="2">
-      <t>モジ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>ヒョウジ</t>
-    </rPh>
-    <rPh sb="12" eb="14">
-      <t>サクセイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>タッチパネルを別ウインドウで開くようにする</t>
-    <rPh sb="7" eb="8">
-      <t>ベツ</t>
-    </rPh>
-    <rPh sb="14" eb="15">
-      <t>ヒラ</t>
+    <rPh sb="26" eb="27">
+      <t>ヨ</t>
+    </rPh>
+    <rPh sb="28" eb="29">
+      <t>コ</t>
+    </rPh>
+    <rPh sb="49" eb="51">
+      <t>ジョウブ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -631,11 +586,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DAA1C63A-541D-4CC5-9B3E-578F3C64DDC0}">
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="11.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="47.58203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="76.75" style="1" customWidth="1"/>
     <col min="3" max="16384" width="8.6640625" style="1"/>
   </cols>
   <sheetData>
@@ -655,7 +610,7 @@
         <v>3</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -663,7 +618,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -671,7 +626,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -687,7 +642,7 @@
         <v>3</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -701,49 +656,6 @@
     <row r="8" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="1" t="s">
         <v>3</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>15</v>
       </c>
     </row>
   </sheetData>
